--- a/tables/all_model_results.xlsx
+++ b/tables/all_model_results.xlsx
@@ -561,28 +561,28 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.7305</v>
+        <v>1.73</v>
       </c>
       <c r="D2">
-        <v>0.0974</v>
+        <v>0.0979</v>
       </c>
       <c r="E2">
-        <v>1.5375</v>
+        <v>1.5394</v>
       </c>
       <c r="F2">
-        <v>1.9195</v>
+        <v>1.9205</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>464.32</v>
+        <v>464.08</v>
       </c>
       <c r="I2">
-        <v>365.29</v>
+        <v>366.2</v>
       </c>
       <c r="J2">
-        <v>581.76</v>
+        <v>582.47</v>
       </c>
     </row>
     <row r="3">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.423</v>
+        <v>0.4231</v>
       </c>
       <c r="D3">
-        <v>0.0247</v>
+        <v>0.0249</v>
       </c>
       <c r="E3">
-        <v>0.3748</v>
+        <v>0.3743</v>
       </c>
       <c r="F3">
-        <v>0.4721</v>
+        <v>0.472</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -615,10 +615,10 @@
         <v>52.66</v>
       </c>
       <c r="I3">
-        <v>45.47</v>
+        <v>45.4</v>
       </c>
       <c r="J3">
-        <v>60.34</v>
+        <v>60.32</v>
       </c>
     </row>
     <row r="4">
@@ -633,28 +633,28 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.0509</v>
+        <v>-0.0508</v>
       </c>
       <c r="D4">
-        <v>0.0201</v>
+        <v>0.0197</v>
       </c>
       <c r="E4">
-        <v>-0.09039999999999999</v>
+        <v>-0.0895</v>
       </c>
       <c r="F4">
-        <v>-0.0113</v>
+        <v>-0.0123</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>-4.97</v>
+        <v>-4.95</v>
       </c>
       <c r="I4">
-        <v>-8.640000000000001</v>
+        <v>-8.56</v>
       </c>
       <c r="J4">
-        <v>-1.13</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="5">
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.1167</v>
+        <v>-0.1168</v>
       </c>
       <c r="D5">
-        <v>0.0216</v>
+        <v>0.0213</v>
       </c>
       <c r="E5">
         <v>-0.1595</v>
       </c>
       <c r="F5">
-        <v>-0.0751</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>-11.02</v>
+        <v>-11.03</v>
       </c>
       <c r="I5">
         <v>-14.74</v>
       </c>
       <c r="J5">
-        <v>-7.23</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="6">
@@ -705,28 +705,28 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.3134</v>
+        <v>1.3127</v>
       </c>
       <c r="D6">
-        <v>0.189</v>
+        <v>0.1843</v>
       </c>
       <c r="E6">
-        <v>0.9394</v>
+        <v>0.9554</v>
       </c>
       <c r="F6">
-        <v>1.6885</v>
+        <v>1.6811</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>271.88</v>
+        <v>271.62</v>
       </c>
       <c r="I6">
-        <v>155.85</v>
+        <v>159.97</v>
       </c>
       <c r="J6">
-        <v>441.12</v>
+        <v>437.14</v>
       </c>
     </row>
     <row r="7">
@@ -741,28 +741,28 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.3637</v>
+        <v>0.3636</v>
       </c>
       <c r="D7">
-        <v>0.0481</v>
+        <v>0.0468</v>
       </c>
       <c r="E7">
-        <v>0.2687</v>
+        <v>0.2698</v>
       </c>
       <c r="F7">
-        <v>0.4585</v>
+        <v>0.454</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>43.86</v>
+        <v>43.85</v>
       </c>
       <c r="I7">
-        <v>30.83</v>
+        <v>30.97</v>
       </c>
       <c r="J7">
-        <v>58.18</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="8">
@@ -777,28 +777,28 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.0008</v>
+        <v>0.0001</v>
       </c>
       <c r="D8">
-        <v>0.0453</v>
+        <v>0.046</v>
       </c>
       <c r="E8">
-        <v>-0.089</v>
+        <v>-0.0897</v>
       </c>
       <c r="F8">
-        <v>0.08840000000000001</v>
+        <v>0.0898</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="I8">
-        <v>-8.52</v>
+        <v>-8.58</v>
       </c>
       <c r="J8">
-        <v>9.25</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="9">
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.0566</v>
+        <v>-0.0556</v>
       </c>
       <c r="D9">
-        <v>0.0464</v>
+        <v>0.046</v>
       </c>
       <c r="E9">
-        <v>-0.1477</v>
+        <v>-0.146</v>
       </c>
       <c r="F9">
-        <v>0.0354</v>
+        <v>0.0337</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>-5.5</v>
+        <v>-5.41</v>
       </c>
       <c r="I9">
-        <v>-13.73</v>
+        <v>-13.58</v>
       </c>
       <c r="J9">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="10">
@@ -849,28 +849,28 @@
         </is>
       </c>
       <c r="C10">
-        <v>-1.2881</v>
+        <v>-1.2864</v>
       </c>
       <c r="D10">
-        <v>0.351</v>
+        <v>0.3531</v>
       </c>
       <c r="E10">
-        <v>-1.996</v>
+        <v>-1.9976</v>
       </c>
       <c r="F10">
-        <v>-0.6032999999999999</v>
+        <v>-0.6067</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>-72.42</v>
+        <v>-72.37</v>
       </c>
       <c r="I10">
-        <v>-86.41</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="J10">
-        <v>-45.3</v>
+        <v>-45.49</v>
       </c>
     </row>
     <row r="11">
@@ -885,28 +885,28 @@
         </is>
       </c>
       <c r="C11">
-        <v>1.531</v>
+        <v>1.5309</v>
       </c>
       <c r="D11">
-        <v>0.0895</v>
+        <v>0.0898</v>
       </c>
       <c r="E11">
-        <v>1.3581</v>
+        <v>1.3569</v>
       </c>
       <c r="F11">
-        <v>1.7106</v>
+        <v>1.7117</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>362.3</v>
+        <v>362.25</v>
       </c>
       <c r="I11">
-        <v>288.87</v>
+        <v>288.43</v>
       </c>
       <c r="J11">
-        <v>453.21</v>
+        <v>453.84</v>
       </c>
     </row>
     <row r="12">
@@ -921,28 +921,28 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.1053</v>
+        <v>-0.106</v>
       </c>
       <c r="D12">
-        <v>0.0716</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E12">
-        <v>-0.2468</v>
+        <v>-0.2495</v>
       </c>
       <c r="F12">
-        <v>0.0351</v>
+        <v>0.0345</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>-9.99</v>
+        <v>-10.06</v>
       </c>
       <c r="I12">
-        <v>-21.87</v>
+        <v>-22.08</v>
       </c>
       <c r="J12">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="13">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.2528</v>
+        <v>-0.2529</v>
       </c>
       <c r="D13">
-        <v>0.0771</v>
+        <v>0.077</v>
       </c>
       <c r="E13">
-        <v>-0.4068</v>
+        <v>-0.4058</v>
       </c>
       <c r="F13">
-        <v>-0.1058</v>
+        <v>-0.1057</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -975,10 +975,10 @@
         <v>-22.34</v>
       </c>
       <c r="I13">
-        <v>-33.42</v>
+        <v>-33.35</v>
       </c>
       <c r="J13">
-        <v>-10.04</v>
+        <v>-10.03</v>
       </c>
     </row>
     <row r="14">
@@ -993,28 +993,28 @@
         </is>
       </c>
       <c r="C14">
-        <v>-0.7345</v>
+        <v>-0.7448</v>
       </c>
       <c r="D14">
-        <v>0.5034</v>
+        <v>0.5012</v>
       </c>
       <c r="E14">
-        <v>-1.7267</v>
+        <v>-1.7458</v>
       </c>
       <c r="F14">
-        <v>0.2405</v>
+        <v>0.2211</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>-52.03</v>
+        <v>-52.52</v>
       </c>
       <c r="I14">
-        <v>-82.20999999999999</v>
+        <v>-82.55</v>
       </c>
       <c r="J14">
-        <v>27.19</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="15">
@@ -1029,28 +1029,28 @@
         </is>
       </c>
       <c r="C15">
-        <v>1.7609</v>
+        <v>1.7642</v>
       </c>
       <c r="D15">
-        <v>0.1284</v>
+        <v>0.1277</v>
       </c>
       <c r="E15">
-        <v>1.5144</v>
+        <v>1.5181</v>
       </c>
       <c r="F15">
-        <v>2.0124</v>
+        <v>2.0201</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>481.79</v>
+        <v>483.68</v>
       </c>
       <c r="I15">
-        <v>354.68</v>
+        <v>356.35</v>
       </c>
       <c r="J15">
-        <v>648.13</v>
+        <v>653.92</v>
       </c>
     </row>
     <row r="16">
@@ -1065,28 +1065,28 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.07580000000000001</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="D16">
-        <v>0.1007</v>
+        <v>0.1016</v>
       </c>
       <c r="E16">
-        <v>-0.273</v>
+        <v>-0.2796</v>
       </c>
       <c r="F16">
-        <v>0.1198</v>
+        <v>0.12</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>-7.3</v>
+        <v>-7.44</v>
       </c>
       <c r="I16">
-        <v>-23.89</v>
+        <v>-24.39</v>
       </c>
       <c r="J16">
-        <v>12.72</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="17">
@@ -1101,28 +1101,28 @@
         </is>
       </c>
       <c r="C17">
-        <v>-0.2993</v>
+        <v>-0.2998</v>
       </c>
       <c r="D17">
-        <v>0.1069</v>
+        <v>0.1073</v>
       </c>
       <c r="E17">
-        <v>-0.5145</v>
+        <v>-0.5143</v>
       </c>
       <c r="F17">
-        <v>-0.0949</v>
+        <v>-0.094</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>-25.87</v>
+        <v>-25.91</v>
       </c>
       <c r="I17">
-        <v>-40.22</v>
+        <v>-40.21</v>
       </c>
       <c r="J17">
-        <v>-9.06</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="C18">
-        <v>-0.4866</v>
+        <v>-0.4874</v>
       </c>
       <c r="D18">
-        <v>0.041</v>
+        <v>0.0414</v>
       </c>
       <c r="E18">
-        <v>-0.5674</v>
+        <v>-0.5699</v>
       </c>
       <c r="F18">
-        <v>-0.4069</v>
+        <v>-0.4077</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>-38.53</v>
+        <v>-38.58</v>
       </c>
       <c r="I18">
-        <v>-43.3</v>
+        <v>-43.44</v>
       </c>
       <c r="J18">
-        <v>-33.43</v>
+        <v>-33.48</v>
       </c>
     </row>
     <row r="19">
@@ -1173,28 +1173,28 @@
         </is>
       </c>
       <c r="C19">
-        <v>-0.0348</v>
+        <v>-0.0346</v>
       </c>
       <c r="D19">
-        <v>0.0374</v>
+        <v>0.0376</v>
       </c>
       <c r="E19">
-        <v>-0.1084</v>
+        <v>-0.1094</v>
       </c>
       <c r="F19">
-        <v>0.0374</v>
+        <v>0.039</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>-3.42</v>
+        <v>-3.4</v>
       </c>
       <c r="I19">
-        <v>-10.27</v>
+        <v>-10.37</v>
       </c>
       <c r="J19">
-        <v>3.81</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="20">
@@ -1209,28 +1209,28 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.07290000000000001</v>
+        <v>-0.0728</v>
       </c>
       <c r="D20">
-        <v>0.0385</v>
+        <v>0.0387</v>
       </c>
       <c r="E20">
-        <v>-0.148</v>
+        <v>-0.1487</v>
       </c>
       <c r="F20">
-        <v>0.002</v>
+        <v>0.0035</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>-7.03</v>
+        <v>-7.02</v>
       </c>
       <c r="I20">
-        <v>-13.75</v>
+        <v>-13.82</v>
       </c>
       <c r="J20">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="21">
@@ -1245,28 +1245,28 @@
         </is>
       </c>
       <c r="C21">
-        <v>-0.8023</v>
+        <v>-0.8028</v>
       </c>
       <c r="D21">
-        <v>0.054</v>
+        <v>0.0531</v>
       </c>
       <c r="E21">
-        <v>-0.9104</v>
+        <v>-0.9081</v>
       </c>
       <c r="F21">
-        <v>-0.6987</v>
+        <v>-0.6997</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>-55.17</v>
+        <v>-55.19</v>
       </c>
       <c r="I21">
-        <v>-59.76</v>
+        <v>-59.67</v>
       </c>
       <c r="J21">
-        <v>-50.28</v>
+        <v>-50.33</v>
       </c>
     </row>
     <row r="22">
@@ -1281,28 +1281,28 @@
         </is>
       </c>
       <c r="C22">
-        <v>-0.0417</v>
+        <v>-0.0405</v>
       </c>
       <c r="D22">
-        <v>0.0572</v>
+        <v>0.0553</v>
       </c>
       <c r="E22">
-        <v>-0.1538</v>
+        <v>-0.1495</v>
       </c>
       <c r="F22">
-        <v>0.0697</v>
+        <v>0.0669</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>-4.09</v>
+        <v>-3.97</v>
       </c>
       <c r="I22">
-        <v>-14.26</v>
+        <v>-13.89</v>
       </c>
       <c r="J22">
-        <v>7.21</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="23">
@@ -1317,28 +1317,28 @@
         </is>
       </c>
       <c r="C23">
-        <v>-0.07480000000000001</v>
+        <v>-0.0733</v>
       </c>
       <c r="D23">
-        <v>0.0613</v>
+        <v>0.0594</v>
       </c>
       <c r="E23">
-        <v>-0.1966</v>
+        <v>-0.1908</v>
       </c>
       <c r="F23">
-        <v>0.0431</v>
+        <v>0.0422</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>-7.2</v>
+        <v>-7.07</v>
       </c>
       <c r="I23">
-        <v>-17.85</v>
+        <v>-17.37</v>
       </c>
       <c r="J23">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
     </row>
   </sheetData>
@@ -2259,28 +2259,28 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.746</v>
+        <v>1.7874</v>
       </c>
       <c r="D2">
-        <v>0.0597</v>
+        <v>0.0587</v>
       </c>
       <c r="E2">
-        <v>1.6292</v>
+        <v>1.6732</v>
       </c>
       <c r="F2">
-        <v>1.8619</v>
+        <v>1.9023</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>473.17</v>
+        <v>497.4</v>
       </c>
       <c r="I2">
-        <v>409.98</v>
+        <v>432.94</v>
       </c>
       <c r="J2">
-        <v>543.59</v>
+        <v>570.12</v>
       </c>
     </row>
     <row r="3">
@@ -2298,10 +2298,10 @@
         <v>0.3996</v>
       </c>
       <c r="D3">
-        <v>0.0148</v>
+        <v>0.0147</v>
       </c>
       <c r="E3">
-        <v>0.3706</v>
+        <v>0.3705</v>
       </c>
       <c r="F3">
         <v>0.4286</v>
@@ -2310,10 +2310,10 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>49.12</v>
+        <v>49.13</v>
       </c>
       <c r="I3">
-        <v>44.86</v>
+        <v>44.85</v>
       </c>
       <c r="J3">
         <v>53.51</v>
@@ -2327,32 +2327,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>h2_2011_categoryremaineduninfested</t>
+          <t>h2_2011_categorygainedinfestation</t>
         </is>
       </c>
       <c r="C4">
-        <v>0.0416</v>
+        <v>-0.0418</v>
       </c>
       <c r="D4">
         <v>0.0146</v>
       </c>
       <c r="E4">
-        <v>0.0128</v>
+        <v>-0.0703</v>
       </c>
       <c r="F4">
-        <v>0.0697</v>
+        <v>-0.0126</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>4.25</v>
+        <v>-4.09</v>
       </c>
       <c r="I4">
-        <v>1.29</v>
+        <v>-6.79</v>
       </c>
       <c r="J4">
-        <v>7.21</v>
+        <v>-1.25</v>
       </c>
     </row>
   </sheetData>

--- a/tables/all_model_results.xlsx
+++ b/tables/all_model_results.xlsx
@@ -2995,7 +2995,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3048,20 +3048,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>Vm_Intercept</t>
         </is>
       </c>
       <c r="C2">
-        <v>1.79</v>
+        <v>3.96</v>
       </c>
       <c r="D2">
-        <v>0.0587</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>1.67</v>
+        <v>3.83</v>
       </c>
       <c r="F2">
-        <v>1.9</v>
+        <v>4.15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>497</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="3">
@@ -3080,28 +3080,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>log_dbh_2011</t>
+          <t>Vm_h2_2011_categorygainedinfestation</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.4</v>
+        <v>-0.133</v>
       </c>
       <c r="D3">
-        <v>0.0147</v>
+        <v>0.162</v>
       </c>
       <c r="E3">
-        <v>0.371</v>
+        <v>-0.304</v>
       </c>
       <c r="F3">
-        <v>0.429</v>
+        <v>0.0723</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3">
-        <v>49.1</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="4">
@@ -3112,20 +3112,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>h2_2011_categorygainedinfestation</t>
+          <t>x_Intercept</t>
         </is>
       </c>
       <c r="C4">
-        <v>-0.0418</v>
+        <v>0.907</v>
       </c>
       <c r="D4">
-        <v>0.0146</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="E4">
-        <v>-0.0703</v>
+        <v>0.73</v>
       </c>
       <c r="F4">
-        <v>-0.0126</v>
+        <v>1.07</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3133,7 +3133,103 @@
         </is>
       </c>
       <c r="H4">
-        <v>-4.09</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>x_h2_2011_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.298</v>
+      </c>
+      <c r="D5">
+        <v>0.106</v>
+      </c>
+      <c r="E5">
+        <v>0.0544</v>
+      </c>
+      <c r="F5">
+        <v>0.489</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K_Intercept</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>27.6</v>
+      </c>
+      <c r="D6">
+        <v>4.96</v>
+      </c>
+      <c r="E6">
+        <v>19.7</v>
+      </c>
+      <c r="F6">
+        <v>39</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>98400000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K_h2_2011_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>38.9</v>
+      </c>
+      <c r="D7">
+        <v>15.3</v>
+      </c>
+      <c r="E7">
+        <v>12.4</v>
+      </c>
+      <c r="F7">
+        <v>71.8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>7.6E+18</v>
       </c>
     </row>
   </sheetData>

--- a/tables/all_model_results.xlsx
+++ b/tables/all_model_results.xlsx
@@ -9,16 +9,13 @@
   <sheets>
     <sheet name="Sample_sizes" sheetId="1" r:id="rId1"/>
     <sheet name="H1_fixed_effects" sheetId="2" r:id="rId2"/>
-    <sheet name="H1_slenderness_ANOVA" sheetId="3" r:id="rId3"/>
-    <sheet name="H1_slenderness_means" sheetId="4" r:id="rId4"/>
-    <sheet name="H1_PAI_fixed_effects" sheetId="5" r:id="rId5"/>
-    <sheet name="H2_fixed_effects" sheetId="6" r:id="rId6"/>
-    <sheet name="H2_slenderness_ANOVA" sheetId="7" r:id="rId7"/>
-    <sheet name="H2_slenderness_means" sheetId="8" r:id="rId8"/>
-    <sheet name="H2_2011_height" sheetId="9" r:id="rId9"/>
-    <sheet name="H2b_OLS_pvalues" sheetId="10" r:id="rId10"/>
-    <sheet name="Model_specifications" sheetId="11" r:id="rId11"/>
-    <sheet name="Height_model_comparison" sheetId="12" r:id="rId12"/>
+    <sheet name="H1_slenderness_brms" sheetId="3" r:id="rId3"/>
+    <sheet name="H1_PAI_fixed_effects" sheetId="4" r:id="rId4"/>
+    <sheet name="H2_fixed_effects" sheetId="5" r:id="rId5"/>
+    <sheet name="H2_slenderness_brms" sheetId="6" r:id="rId6"/>
+    <sheet name="H2_2011_height" sheetId="7" r:id="rId7"/>
+    <sheet name="H2b_OLS_pvalues" sheetId="8" r:id="rId8"/>
+    <sheet name="Model_specifications" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,694 +493,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>p (pathway type)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>p (Active vs Passive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Crown depth</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.222</v>
-      </c>
-      <c r="C2">
-        <v>0.398</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Crown projected area</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0.899</v>
-      </c>
-      <c r="C3">
-        <v>0.0616</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Crown volume</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.617</v>
-      </c>
-      <c r="C4">
-        <v>0.0456</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tree height</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.165</v>
-      </c>
-      <c r="C5">
-        <v>0.618</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Response variable</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Model type</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed effects</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Random effects</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>n obs</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n species</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>log(Tree height)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>log(DBH) + H1_category</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>251</v>
-      </c>
-      <c r="G2">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>log(Crown projected area)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>log(DBH) + H1_category</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F3">
-        <v>251</v>
-      </c>
-      <c r="G3">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>log(Crown volume)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>log(DBH) + H1_category</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F4">
-        <v>251</v>
-      </c>
-      <c r="G4">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>log(Crown depth)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>log(DBH) + H1_category</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F5">
-        <v>251</v>
-      </c>
-      <c r="G5">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Slenderness (height/DBH)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>One-way ANOVA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>H1_category</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>251</v>
-      </c>
-      <c r="G6">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>log(Crown base height ratio)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>H1_category</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F7">
-        <v>251</v>
-      </c>
-      <c r="G7">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>H1 PAI</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>log(PAI tree only)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>infest_cat + log(DBH)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>(1|Species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F8">
-        <v>575</v>
-      </c>
-      <c r="G8">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>H2 TLS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>log(Tree height)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>log(DBH) + H2_category</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F9">
-        <v>181</v>
-      </c>
-      <c r="G9">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H2 TLS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>log(Crown projected area)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>log(DBH) + H2_category</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F10">
-        <v>181</v>
-      </c>
-      <c r="G10">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H2 TLS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>log(Crown volume)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>log(DBH) + H2_category</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F11">
-        <v>181</v>
-      </c>
-      <c r="G11">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H2 TLS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>log(Crown depth)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>log(DBH) + H2_category</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F12">
-        <v>181</v>
-      </c>
-      <c r="G12">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>H2 TLS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Slenderness (height/DBH)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>One-way ANOVA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>H2_category</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13">
-        <v>181</v>
-      </c>
-      <c r="G13">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>H2 TLS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>log(Crown base height ratio)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>H2_category</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(1|species) + (1|subplot)</t>
-        </is>
-      </c>
-      <c r="F14">
-        <v>181</v>
-      </c>
-      <c r="G14">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>H2 height</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>log(Height 2011)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>brm LMM (Student-t)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>log(DBH 2011) + h2_2011_category</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>(1|species)</t>
-        </is>
-      </c>
-      <c r="F15">
-        <v>414</v>
-      </c>
-      <c r="G15">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>AIC</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>BIC</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ΔAIC vs log-log</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>log(H) ~ log(DBH) [log-log lmer]</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>-272</v>
-      </c>
-      <c r="C2">
-        <v>-247.3</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>← reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MM: Asym ~ H1_category, half ~ 1</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1324.5</v>
-      </c>
-      <c r="C3">
-        <v>1345.6</v>
-      </c>
-      <c r="D3">
-        <v>1596.4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>log-log preferred</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MM: Asym ~ 1, half ~ H1_category</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1323.9</v>
-      </c>
-      <c r="C4">
-        <v>1345.1</v>
-      </c>
-      <c r="D4">
-        <v>1595.9</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>log-log preferred</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H20"/>
@@ -1846,92 +1155,145 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hypothesis</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Term</t>
+          <t>term</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Df</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sum Sq</t>
+          <t>Std. Error</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mean Sq</t>
+          <t>Q2.5</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>F value</t>
+          <t>Q97.5</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p value</t>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>% Effect</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H1 — Slenderness</t>
+          <t>H1 — Slenderness (height/DBH)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H1_category</t>
+          <t>Intercept</t>
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>-0.487</v>
       </c>
       <c r="D2">
-        <v>0.472</v>
+        <v>0.0414</v>
       </c>
       <c r="E2">
-        <v>0.236</v>
+        <v>-0.57</v>
       </c>
       <c r="F2">
-        <v>3.49</v>
-      </c>
-      <c r="G2">
-        <v>0.0319</v>
+        <v>-0.408</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2">
+        <v>-38.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H1 — Slenderness</t>
+          <t>H1 — Slenderness (height/DBH)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Residuals  </t>
+          <t>H1_categoryLostlianas</t>
         </is>
       </c>
       <c r="C3">
-        <v>248</v>
+        <v>-0.0346</v>
       </c>
       <c r="D3">
-        <v>16.7</v>
+        <v>0.0376</v>
       </c>
       <c r="E3">
-        <v>0.0675</v>
+        <v>-0.109</v>
+      </c>
+      <c r="F3">
+        <v>0.039</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H1 — Slenderness (height/DBH)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1_categoryPersistentlyinfested</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>-0.0728</v>
+      </c>
+      <c r="D4">
+        <v>0.0387</v>
+      </c>
+      <c r="E4">
+        <v>-0.149</v>
+      </c>
+      <c r="F4">
+        <v>0.00352</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>-7.02</v>
       </c>
     </row>
   </sheetData>
@@ -1941,153 +1303,177 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>H1_category</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Estimated marginal mean (log)</t>
+          <t>term</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>df</t>
+          <t>Std. Error</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>lower.CL</t>
+          <t>Q2.5</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>upper.CL</t>
+          <t>Q97.5</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>pct_effect</t>
+          <t>Significant</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>% Effect vs baseline</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
+          <t>% Effect</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Never infested</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>-0.484</v>
+          <t>H1 PAI — log(PAI tree only)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.033</v>
+        <v>1.91</v>
       </c>
       <c r="D2">
-        <v>248</v>
+        <v>0.222</v>
       </c>
       <c r="E2">
-        <v>-0.549034402293897</v>
+        <v>1.47</v>
       </c>
       <c r="F2">
-        <v>-0.4190731364049566</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
+        <v>2.34</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>H1 — Slenderness</t>
-        </is>
+        <v>573</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lost lianas</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>-0.532</v>
+          <t>H1 PAI — log(PAI tree only)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>infest_catLight</t>
+        </is>
       </c>
       <c r="C3">
-        <v>0.0274</v>
+        <v>0.0837</v>
       </c>
       <c r="D3">
-        <v>248</v>
+        <v>0.0508</v>
       </c>
       <c r="E3">
-        <v>-0.5861929503002938</v>
+        <v>-0.016</v>
       </c>
       <c r="F3">
-        <v>-0.4783259695039722</v>
-      </c>
-      <c r="G3">
-        <v>-4.7</v>
+        <v>0.183</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="H3">
-        <v>-4.7</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>H1 — Slenderness</t>
-        </is>
+        <v>8.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Persistently infested</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>-0.593</v>
+          <t>H1 PAI — log(PAI tree only)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>infest_catHeavy</t>
+        </is>
       </c>
       <c r="C4">
-        <v>0.0261</v>
+        <v>-0.131</v>
       </c>
       <c r="D4">
-        <v>248</v>
+        <v>0.0542</v>
       </c>
       <c r="E4">
-        <v>-0.6442802747966617</v>
+        <v>-0.236</v>
       </c>
       <c r="F4">
-        <v>-0.5414331439924963</v>
-      </c>
-      <c r="G4">
-        <v>-10.3</v>
+        <v>-0.0254</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="H4">
-        <v>-10.3</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>H1 — Slenderness</t>
-        </is>
+        <v>-12.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>H1 PAI — log(PAI tree only)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>log_dbh</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>-0.203</v>
+      </c>
+      <c r="D5">
+        <v>0.0579</v>
+      </c>
+      <c r="E5">
+        <v>-0.315</v>
+      </c>
+      <c r="F5">
+        <v>-0.0873</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>-18.3</v>
       </c>
     </row>
   </sheetData>
@@ -2097,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2145,7 +1531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H1 PAI — log(PAI tree only)</t>
+          <t>H2 — Tree height</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2154,16 +1540,16 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="D2">
-        <v>0.222</v>
+        <v>0.104</v>
       </c>
       <c r="E2">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2171,103 +1557,423 @@
         </is>
       </c>
       <c r="H2">
-        <v>573</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H1 PAI — log(PAI tree only)</t>
+          <t>H2 — Tree height</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>infest_catLight</t>
+          <t>log_dbh</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.0837</v>
+        <v>0.389</v>
       </c>
       <c r="D3">
-        <v>0.0508</v>
+        <v>0.0269</v>
       </c>
       <c r="E3">
-        <v>-0.016</v>
+        <v>0.338</v>
       </c>
       <c r="F3">
-        <v>0.183</v>
+        <v>0.443</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3">
-        <v>8.73</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H1 PAI — log(PAI tree only)</t>
+          <t>H2 — Tree height</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>infest_catHeavy</t>
+          <t>H2_categorygainedinfestation</t>
         </is>
       </c>
       <c r="C4">
-        <v>-0.131</v>
+        <v>-0.0102</v>
       </c>
       <c r="D4">
-        <v>0.0542</v>
+        <v>0.0179</v>
       </c>
       <c r="E4">
-        <v>-0.236</v>
+        <v>-0.0457</v>
       </c>
       <c r="F4">
-        <v>-0.0254</v>
+        <v>0.0245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4">
-        <v>-12.3</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H1 PAI — log(PAI tree only)</t>
+          <t>H2 — Crown depth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1.36</v>
+      </c>
+      <c r="D5">
+        <v>0.234</v>
+      </c>
+      <c r="E5">
+        <v>0.904</v>
+      </c>
+      <c r="F5">
+        <v>1.82</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H2 — Crown depth</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>log_dbh</t>
         </is>
       </c>
-      <c r="C5">
-        <v>-0.203</v>
-      </c>
-      <c r="D5">
-        <v>0.0579</v>
-      </c>
-      <c r="E5">
-        <v>-0.315</v>
-      </c>
-      <c r="F5">
-        <v>-0.0873</v>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="C6">
+        <v>0.351</v>
+      </c>
+      <c r="D6">
+        <v>0.0609</v>
+      </c>
+      <c r="E6">
+        <v>0.231</v>
+      </c>
+      <c r="F6">
+        <v>0.47</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5">
-        <v>-18.3</v>
+      <c r="H6">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>H2 — Crown depth</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.0155</v>
+      </c>
+      <c r="D7">
+        <v>0.04</v>
+      </c>
+      <c r="E7">
+        <v>-0.0619</v>
+      </c>
+      <c r="F7">
+        <v>0.0948</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>H2 — Crown projected area</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>-1.14</v>
+      </c>
+      <c r="D8">
+        <v>0.348</v>
+      </c>
+      <c r="E8">
+        <v>-1.83</v>
+      </c>
+      <c r="F8">
+        <v>-0.445</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8">
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H2 — Crown projected area</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>log_dbh</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1.48</v>
+      </c>
+      <c r="D9">
+        <v>0.09</v>
+      </c>
+      <c r="E9">
+        <v>1.31</v>
+      </c>
+      <c r="F9">
+        <v>1.66</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H9">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H2 — Crown projected area</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H2_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.0224</v>
+      </c>
+      <c r="D10">
+        <v>0.0587</v>
+      </c>
+      <c r="E10">
+        <v>-0.09329999999999999</v>
+      </c>
+      <c r="F10">
+        <v>0.138</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H2 — Crown volume</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>-0.477</v>
+      </c>
+      <c r="D11">
+        <v>0.486</v>
+      </c>
+      <c r="E11">
+        <v>-1.44</v>
+      </c>
+      <c r="F11">
+        <v>0.462</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>-38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H2 — Crown volume</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>log_dbh</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>1.69</v>
+      </c>
+      <c r="D12">
+        <v>0.126</v>
+      </c>
+      <c r="E12">
+        <v>1.45</v>
+      </c>
+      <c r="F12">
+        <v>1.94</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H2 — Crown volume</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H2_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.0299</v>
+      </c>
+      <c r="D13">
+        <v>0.0805</v>
+      </c>
+      <c r="E13">
+        <v>-0.129</v>
+      </c>
+      <c r="F13">
+        <v>0.189</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H2 — Crown base height ratio</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>-0.805</v>
+      </c>
+      <c r="D14">
+        <v>0.0464</v>
+      </c>
+      <c r="E14">
+        <v>-0.899</v>
+      </c>
+      <c r="F14">
+        <v>-0.715</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>-55.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H2 — Crown base height ratio</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H2_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>-0.0287</v>
+      </c>
+      <c r="D15">
+        <v>0.0487</v>
+      </c>
+      <c r="E15">
+        <v>-0.125</v>
+      </c>
+      <c r="F15">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15">
+        <v>-2.83</v>
       </c>
     </row>
   </sheetData>
@@ -2277,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2325,7 +2031,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H2 — Tree height</t>
+          <t>H2 — Slenderness (height/DBH)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2334,16 +2040,16 @@
         </is>
       </c>
       <c r="C2">
-        <v>1.85</v>
+        <v>-0.473</v>
       </c>
       <c r="D2">
-        <v>0.104</v>
+        <v>0.0389</v>
       </c>
       <c r="E2">
-        <v>1.64</v>
+        <v>-0.549</v>
       </c>
       <c r="F2">
-        <v>2.05</v>
+        <v>-0.396</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2351,423 +2057,39 @@
         </is>
       </c>
       <c r="H2">
-        <v>535</v>
+        <v>-37.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H2 — Tree height</t>
+          <t>H2 — Slenderness (height/DBH)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>log_dbh</t>
+          <t>H2_categorygainedinfestation</t>
         </is>
       </c>
       <c r="C3">
-        <v>0.389</v>
+        <v>-0.0431</v>
       </c>
       <c r="D3">
-        <v>0.0269</v>
+        <v>0.0361</v>
       </c>
       <c r="E3">
-        <v>0.338</v>
+        <v>-0.114</v>
       </c>
       <c r="F3">
-        <v>0.443</v>
+        <v>0.028</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3">
-        <v>47.6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>H2 — Tree height</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>H2_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>-0.0102</v>
-      </c>
-      <c r="D4">
-        <v>0.0179</v>
-      </c>
-      <c r="E4">
-        <v>-0.0457</v>
-      </c>
-      <c r="F4">
-        <v>0.0245</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>H2 — Crown depth</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1.36</v>
-      </c>
-      <c r="D5">
-        <v>0.234</v>
-      </c>
-      <c r="E5">
-        <v>0.904</v>
-      </c>
-      <c r="F5">
-        <v>1.82</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>H2 — Crown depth</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>log_dbh</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.351</v>
-      </c>
-      <c r="D6">
-        <v>0.0609</v>
-      </c>
-      <c r="E6">
-        <v>0.231</v>
-      </c>
-      <c r="F6">
-        <v>0.47</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6">
-        <v>42.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>H2 — Crown depth</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>H2_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.0155</v>
-      </c>
-      <c r="D7">
-        <v>0.04</v>
-      </c>
-      <c r="E7">
-        <v>-0.0619</v>
-      </c>
-      <c r="F7">
-        <v>0.0948</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>H2 — Crown projected area</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>-1.14</v>
-      </c>
-      <c r="D8">
-        <v>0.348</v>
-      </c>
-      <c r="E8">
-        <v>-1.83</v>
-      </c>
-      <c r="F8">
-        <v>-0.445</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H8">
-        <v>-68</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>H2 — Crown projected area</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>log_dbh</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>1.48</v>
-      </c>
-      <c r="D9">
-        <v>0.09</v>
-      </c>
-      <c r="E9">
-        <v>1.31</v>
-      </c>
-      <c r="F9">
-        <v>1.66</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>H2 — Crown projected area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>H2_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>0.0224</v>
-      </c>
-      <c r="D10">
-        <v>0.0587</v>
-      </c>
-      <c r="E10">
-        <v>-0.09329999999999999</v>
-      </c>
-      <c r="F10">
-        <v>0.138</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H10">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>H2 — Crown volume</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>-0.477</v>
-      </c>
-      <c r="D11">
-        <v>0.486</v>
-      </c>
-      <c r="E11">
-        <v>-1.44</v>
-      </c>
-      <c r="F11">
-        <v>0.462</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H11">
-        <v>-38</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>H2 — Crown volume</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>log_dbh</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>1.69</v>
-      </c>
-      <c r="D12">
-        <v>0.126</v>
-      </c>
-      <c r="E12">
-        <v>1.45</v>
-      </c>
-      <c r="F12">
-        <v>1.94</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>H2 — Crown volume</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H2_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0.0299</v>
-      </c>
-      <c r="D13">
-        <v>0.0805</v>
-      </c>
-      <c r="E13">
-        <v>-0.129</v>
-      </c>
-      <c r="F13">
-        <v>0.189</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H13">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>H2 — Crown base height ratio</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>-0.805</v>
-      </c>
-      <c r="D14">
-        <v>0.0464</v>
-      </c>
-      <c r="E14">
-        <v>-0.899</v>
-      </c>
-      <c r="F14">
-        <v>-0.715</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14">
-        <v>-55.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>H2 — Crown base height ratio</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H2_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>-0.0287</v>
-      </c>
-      <c r="D15">
-        <v>0.0487</v>
-      </c>
-      <c r="E15">
-        <v>-0.125</v>
-      </c>
-      <c r="F15">
-        <v>0.06560000000000001</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15">
-        <v>-2.83</v>
+        <v>-4.22</v>
       </c>
     </row>
   </sheetData>
@@ -2777,92 +2099,241 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hypothesis</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Term</t>
+          <t>term</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Df</t>
+          <t>Estimate</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sum Sq</t>
+          <t>Std. Error</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mean Sq</t>
+          <t>Q2.5</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>F value</t>
+          <t>Q97.5</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>p value</t>
+          <t>Significant</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>% Effect</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H2 — Slenderness</t>
+          <t>H2 height 2011 — log(height 2011)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>H2_category</t>
+          <t>Vm_Intercept</t>
         </is>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3.96</v>
       </c>
       <c r="D2">
-        <v>0.344</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>0.344</v>
+        <v>3.83</v>
       </c>
       <c r="F2">
-        <v>4.71</v>
-      </c>
-      <c r="G2">
-        <v>0.0312</v>
+        <v>4.15</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2">
+        <v>5170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H2 — Slenderness</t>
+          <t>H2 height 2011 — log(height 2011)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Residuals  </t>
+          <t>Vm_h2_2011_categorygainedinfestation</t>
         </is>
       </c>
       <c r="C3">
-        <v>179</v>
+        <v>-0.133</v>
       </c>
       <c r="D3">
-        <v>13.1</v>
+        <v>0.162</v>
       </c>
       <c r="E3">
-        <v>0.073</v>
+        <v>-0.304</v>
+      </c>
+      <c r="F3">
+        <v>0.0723</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>x_Intercept</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.907</v>
+      </c>
+      <c r="D4">
+        <v>0.09130000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.73</v>
+      </c>
+      <c r="F4">
+        <v>1.07</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>x_h2_2011_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.298</v>
+      </c>
+      <c r="D5">
+        <v>0.106</v>
+      </c>
+      <c r="E5">
+        <v>0.0544</v>
+      </c>
+      <c r="F5">
+        <v>0.489</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>K_Intercept</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>27.6</v>
+      </c>
+      <c r="D6">
+        <v>4.96</v>
+      </c>
+      <c r="E6">
+        <v>19.7</v>
+      </c>
+      <c r="F6">
+        <v>39</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6">
+        <v>98400000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>H2 height 2011 — log(height 2011)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>K_h2_2011_categorygainedinfestation</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>38.9</v>
+      </c>
+      <c r="D7">
+        <v>15.3</v>
+      </c>
+      <c r="E7">
+        <v>12.4</v>
+      </c>
+      <c r="F7">
+        <v>71.8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>7.6E+18</v>
       </c>
     </row>
   </sheetData>
@@ -2872,120 +2343,76 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>H2_category</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Estimated marginal mean (log)</t>
+          <t>p (pathway type)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>lower.CL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>upper.CL</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pct_effect</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>% Effect vs baseline</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Hypothesis</t>
+          <t>p (Active vs Passive)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>remained uninfested</t>
+          <t>Crown depth</t>
         </is>
       </c>
       <c r="B2">
-        <v>-0.464</v>
+        <v>0.222</v>
       </c>
       <c r="C2">
-        <v>0.0255</v>
-      </c>
-      <c r="D2">
-        <v>179</v>
-      </c>
-      <c r="E2">
-        <v>-0.5146394085781849</v>
-      </c>
-      <c r="F2">
-        <v>-0.4138841671396957</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>H2 — Slenderness</t>
-        </is>
+        <v>0.398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gained infestation</t>
+          <t>Crown projected area</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.554</v>
+        <v>0.899</v>
       </c>
       <c r="C3">
-        <v>0.0325</v>
-      </c>
-      <c r="D3">
-        <v>179</v>
-      </c>
-      <c r="E3">
-        <v>-0.6182252568288972</v>
-      </c>
-      <c r="F3">
-        <v>-0.489858634465011</v>
-      </c>
-      <c r="G3">
-        <v>-8.6</v>
-      </c>
-      <c r="H3">
-        <v>-8.6</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>H2 — Slenderness</t>
-        </is>
+        <v>0.0616</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Crown volume</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.617</v>
+      </c>
+      <c r="C4">
+        <v>0.0456</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tree height</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.165</v>
+      </c>
+      <c r="C5">
+        <v>0.618</v>
       </c>
     </row>
   </sheetData>
@@ -2995,241 +2422,506 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Hypothesis</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>term</t>
+          <t>Response variable</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Estimate</t>
+          <t>Model type</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Std. Error</t>
+          <t>Fixed effects</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Q2.5</t>
+          <t>Random effects</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Q97.5</t>
+          <t>n obs</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Significant</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>% Effect</t>
+          <t>n species</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H2 height 2011 — log(height 2011)</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vm_Intercept</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>3.96</v>
-      </c>
-      <c r="D2">
-        <v>0.109</v>
-      </c>
-      <c r="E2">
-        <v>3.83</v>
+          <t>log(Tree height)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>log(DBH) + H1_category</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
       </c>
       <c r="F2">
-        <v>4.15</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2">
-        <v>5170</v>
+        <v>251</v>
+      </c>
+      <c r="G2">
+        <v>67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H2 height 2011 — log(height 2011)</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vm_h2_2011_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>-0.133</v>
-      </c>
-      <c r="D3">
-        <v>0.162</v>
-      </c>
-      <c r="E3">
-        <v>-0.304</v>
+          <t>log(Crown projected area)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>log(DBH) + H1_category</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
       </c>
       <c r="F3">
-        <v>0.0723</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H3">
-        <v>-12.4</v>
+        <v>251</v>
+      </c>
+      <c r="G3">
+        <v>67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H2 height 2011 — log(height 2011)</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>x_Intercept</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.907</v>
-      </c>
-      <c r="D4">
-        <v>0.09130000000000001</v>
-      </c>
-      <c r="E4">
-        <v>0.73</v>
+          <t>log(Crown volume)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>log(DBH) + H1_category</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
       </c>
       <c r="F4">
-        <v>1.07</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4">
-        <v>148</v>
+        <v>251</v>
+      </c>
+      <c r="G4">
+        <v>67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H2 height 2011 — log(height 2011)</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>x_h2_2011_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>0.298</v>
-      </c>
-      <c r="D5">
-        <v>0.106</v>
-      </c>
-      <c r="E5">
-        <v>0.0544</v>
+          <t>log(Crown depth)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>log(DBH) + H1_category</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
       </c>
       <c r="F5">
-        <v>0.489</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5">
-        <v>34.7</v>
+        <v>251</v>
+      </c>
+      <c r="G5">
+        <v>67</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H2 height 2011 — log(height 2011)</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>K_Intercept</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>27.6</v>
-      </c>
-      <c r="D6">
-        <v>4.96</v>
-      </c>
-      <c r="E6">
-        <v>19.7</v>
+          <t>Slenderness (height/DBH)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>H1_category</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
       </c>
       <c r="F6">
-        <v>39</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6">
-        <v>98400000000000</v>
+        <v>251</v>
+      </c>
+      <c r="G6">
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H2 height 2011 — log(height 2011)</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>K_h2_2011_categorygainedinfestation</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>38.9</v>
-      </c>
-      <c r="D7">
-        <v>15.3</v>
-      </c>
-      <c r="E7">
-        <v>12.4</v>
+          <t>log(Crown base height ratio)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>H1_category</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
       </c>
       <c r="F7">
-        <v>71.8</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7">
-        <v>7.6E+18</v>
+        <v>251</v>
+      </c>
+      <c r="G7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>H1 PAI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>log(PAI tree only)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>infest_cat + log(DBH)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(1|Species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>575</v>
+      </c>
+      <c r="G8">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H2 TLS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>log(Tree height)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>log(DBH) + H2_category</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>181</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H2 TLS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>log(Crown projected area)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>log(DBH) + H2_category</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>181</v>
+      </c>
+      <c r="G10">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H2 TLS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>log(Crown volume)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>log(DBH) + H2_category</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>181</v>
+      </c>
+      <c r="G11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H2 TLS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>log(Crown depth)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>log(DBH) + H2_category</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>181</v>
+      </c>
+      <c r="G12">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H2 TLS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Slenderness (height/DBH)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>H2_category</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>181</v>
+      </c>
+      <c r="G13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H2 TLS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>log(Crown base height ratio)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>brm LMM (Student-t)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>H2_category</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(1|species) + (1|subplot)</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>181</v>
+      </c>
+      <c r="G14">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H2 height</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Height 2011 (MM8 nonlinear)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>brm NLM (Gaussian) — MM8</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Vm + x + K ~ h2_2011_category</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>(1|species)</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>414</v>
+      </c>
+      <c r="G15">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
